--- a/data/Google Sheet/Archipelago_Games_17_08_2026.xlsx
+++ b/data/Google Sheet/Archipelago_Games_17_08_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pomme\Documents\Projects\the-independent-archipelago\data\Google Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{AB718A48-1E4A-405B-899D-4D32BD8A36B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67C8EC30-E598-4247-84A2-642AB752E474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="5085" windowWidth="29040" windowHeight="15720" xr2:uid="{1AEC296A-4F2D-4DB2-93B1-A539F09C789B}"/>
+    <workbookView xWindow="38400" yWindow="5205" windowWidth="28800" windowHeight="15345" xr2:uid="{1AEC296A-4F2D-4DB2-93B1-A539F09C789B}"/>
   </bookViews>
   <sheets>
     <sheet name="Archipelago_Games_17_08_2026" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2040" uniqueCount="711">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2202" uniqueCount="792">
   <si>
     <t>Game</t>
   </si>
@@ -2221,6 +2221,249 @@
       </rPr>
       <t>YouTube</t>
     </r>
+  </si>
+  <si>
+    <t>Adventure</t>
+  </si>
+  <si>
+    <t>APQuest</t>
+  </si>
+  <si>
+    <t>Aquaria</t>
+  </si>
+  <si>
+    <t>Blasphemous</t>
+  </si>
+  <si>
+    <t>Bomb Rush Cyberfunk</t>
+  </si>
+  <si>
+    <t>Bumper Stickers</t>
+  </si>
+  <si>
+    <t>Castlevania - Circle of the Moon</t>
+  </si>
+  <si>
+    <t>Castlevania 64</t>
+  </si>
+  <si>
+    <t>Celeste (Open World)</t>
+  </si>
+  <si>
+    <t>Celeste 64</t>
+  </si>
+  <si>
+    <t>ChecksFinder</t>
+  </si>
+  <si>
+    <t>Choo Choo Charles</t>
+  </si>
+  <si>
+    <t>Civilization VI</t>
+  </si>
+  <si>
+    <t>Dark Souls III</t>
+  </si>
+  <si>
+    <t>DLCQuest</t>
+  </si>
+  <si>
+    <t>Donkey Kong Country 3</t>
+  </si>
+  <si>
+    <t>DOOM 1993</t>
+  </si>
+  <si>
+    <t>DOOM II</t>
+  </si>
+  <si>
+    <t>Earthbound</t>
+  </si>
+  <si>
+    <t>Factorio</t>
+  </si>
+  <si>
+    <t>Faxanadu</t>
+  </si>
+  <si>
+    <t>Final Fantasy</t>
+  </si>
+  <si>
+    <t>Final Fantasy Mystic Quest</t>
+  </si>
+  <si>
+    <t>A Hat in Time</t>
+  </si>
+  <si>
+    <t>Heretic</t>
+  </si>
+  <si>
+    <t>Hollow Knight</t>
+  </si>
+  <si>
+    <t>Hylics 2</t>
+  </si>
+  <si>
+    <t>Inscryption</t>
+  </si>
+  <si>
+    <t>Jak and Daxter: The Precursor Legacy</t>
+  </si>
+  <si>
+    <t>Kingdom Hearts</t>
+  </si>
+  <si>
+    <t>Kingdom Hearts 2</t>
+  </si>
+  <si>
+    <t>Kirby's Dream Land 3</t>
+  </si>
+  <si>
+    <t>Landstalker - The Treasures of King Nole</t>
+  </si>
+  <si>
+    <t>The Legend of Zelda</t>
+  </si>
+  <si>
+    <t>The Legend of Zelda: A Link to the Past</t>
+  </si>
+  <si>
+    <t>The Legend of Zelda: Links Awakening DX</t>
+  </si>
+  <si>
+    <t>The Legend of Zelda: Ocarina of Time</t>
+  </si>
+  <si>
+    <t>The Legend of Zelda: The Wind Waker</t>
+  </si>
+  <si>
+    <t>Lingo</t>
+  </si>
+  <si>
+    <t>Lufia II Ancient Cave</t>
+  </si>
+  <si>
+    <t>Mario &amp; Luigi Superstar Saga</t>
+  </si>
+  <si>
+    <t>Mega Man 2</t>
+  </si>
+  <si>
+    <t>Mega Man 3</t>
+  </si>
+  <si>
+    <t>MegaMan Battle Network 3</t>
+  </si>
+  <si>
+    <t>Meritous</t>
+  </si>
+  <si>
+    <t>The Messenger</t>
+  </si>
+  <si>
+    <t>Muse Dash</t>
+  </si>
+  <si>
+    <t>Noita</t>
+  </si>
+  <si>
+    <t>Old School Runescape</t>
+  </si>
+  <si>
+    <t>Overcooked! 2</t>
+  </si>
+  <si>
+    <t>Paint</t>
+  </si>
+  <si>
+    <t>Pokemon Emerald</t>
+  </si>
+  <si>
+    <t>Pokemon Red and Blue</t>
+  </si>
+  <si>
+    <t>Raft</t>
+  </si>
+  <si>
+    <t>Risk of Rain 2</t>
+  </si>
+  <si>
+    <t>Satisfactory</t>
+  </si>
+  <si>
+    <t>Saving Princess</t>
+  </si>
+  <si>
+    <t>Secret of Evermore</t>
+  </si>
+  <si>
+    <t>shapez</t>
+  </si>
+  <si>
+    <t>Shivers</t>
+  </si>
+  <si>
+    <t>A Short Hike</t>
+  </si>
+  <si>
+    <t>SMZ3</t>
+  </si>
+  <si>
+    <t>Sonic Adventure 2 Battle</t>
+  </si>
+  <si>
+    <t>Starcraft 2</t>
+  </si>
+  <si>
+    <t>Stardew Valley</t>
+  </si>
+  <si>
+    <t>Subnautica</t>
+  </si>
+  <si>
+    <t>Super Mario 64</t>
+  </si>
+  <si>
+    <t>Super Mario Land 2: The Golden Coins</t>
+  </si>
+  <si>
+    <t>Super Mario World</t>
+  </si>
+  <si>
+    <t>Super Metroid</t>
+  </si>
+  <si>
+    <t>Terraria</t>
+  </si>
+  <si>
+    <t>Timespinner</t>
+  </si>
+  <si>
+    <t>TUNIC</t>
+  </si>
+  <si>
+    <t>Undertale</t>
+  </si>
+  <si>
+    <t>VVVVVV</t>
+  </si>
+  <si>
+    <t>Wargroove</t>
+  </si>
+  <si>
+    <t>The Witness</t>
+  </si>
+  <si>
+    <t>Yacht Dice</t>
+  </si>
+  <si>
+    <t>Yoshi's Island</t>
+  </si>
+  <si>
+    <t>Yu-Gi-Oh! 2006</t>
+  </si>
+  <si>
+    <t>Zillion</t>
   </si>
 </sst>
 </file>
@@ -2820,7 +3063,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2884,6 +3127,15 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="12" xfId="42" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="12" xfId="42" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -3261,7 +3513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA2815DF-B9FB-49EB-8EF6-EAC0843BFA58}">
-  <dimension ref="A1:C687"/>
+  <dimension ref="A1:C768"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -10780,6 +11032,735 @@
         <v>699</v>
       </c>
       <c r="C687" s="9"/>
+    </row>
+    <row r="688" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A688" s="9" t="s">
+        <v>711</v>
+      </c>
+      <c r="B688" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C688" s="6"/>
+    </row>
+    <row r="689" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A689" s="10" t="s">
+        <v>712</v>
+      </c>
+      <c r="B689" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C689" s="4"/>
+    </row>
+    <row r="690" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A690" s="9" t="s">
+        <v>713</v>
+      </c>
+      <c r="B690" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C690" s="6"/>
+    </row>
+    <row r="691" spans="1:3" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A691" s="10" t="s">
+        <v>714</v>
+      </c>
+      <c r="B691" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C691" s="4"/>
+    </row>
+    <row r="692" spans="1:3" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A692" s="9" t="s">
+        <v>715</v>
+      </c>
+      <c r="B692" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C692" s="6"/>
+    </row>
+    <row r="693" spans="1:3" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A693" s="10" t="s">
+        <v>716</v>
+      </c>
+      <c r="B693" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C693" s="4"/>
+    </row>
+    <row r="694" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A694" s="22" t="s">
+        <v>717</v>
+      </c>
+      <c r="B694" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C694" s="23"/>
+    </row>
+    <row r="695" spans="1:3" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A695" s="10" t="s">
+        <v>718</v>
+      </c>
+      <c r="B695" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C695" s="4"/>
+    </row>
+    <row r="696" spans="1:3" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A696" s="9" t="s">
+        <v>719</v>
+      </c>
+      <c r="B696" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C696" s="6"/>
+    </row>
+    <row r="697" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A697" s="10" t="s">
+        <v>720</v>
+      </c>
+      <c r="B697" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C697" s="4"/>
+    </row>
+    <row r="698" spans="1:3" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A698" s="9" t="s">
+        <v>721</v>
+      </c>
+      <c r="B698" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C698" s="6"/>
+    </row>
+    <row r="699" spans="1:3" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A699" s="10" t="s">
+        <v>722</v>
+      </c>
+      <c r="B699" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C699" s="4"/>
+    </row>
+    <row r="700" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A700" s="22" t="s">
+        <v>723</v>
+      </c>
+      <c r="B700" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C700" s="23"/>
+    </row>
+    <row r="701" spans="1:3" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A701" s="10" t="s">
+        <v>724</v>
+      </c>
+      <c r="B701" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C701" s="4"/>
+    </row>
+    <row r="702" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A702" s="9" t="s">
+        <v>725</v>
+      </c>
+      <c r="B702" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C702" s="6"/>
+    </row>
+    <row r="703" spans="1:3" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A703" s="10" t="s">
+        <v>726</v>
+      </c>
+      <c r="B703" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C703" s="4"/>
+    </row>
+    <row r="704" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A704" s="9" t="s">
+        <v>727</v>
+      </c>
+      <c r="B704" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C704" s="6"/>
+    </row>
+    <row r="705" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A705" s="10" t="s">
+        <v>728</v>
+      </c>
+      <c r="B705" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C705" s="4"/>
+    </row>
+    <row r="706" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A706" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="B706" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C706" s="6"/>
+    </row>
+    <row r="707" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A707" s="10" t="s">
+        <v>730</v>
+      </c>
+      <c r="B707" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C707" s="4"/>
+    </row>
+    <row r="708" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A708" s="22" t="s">
+        <v>731</v>
+      </c>
+      <c r="B708" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C708" s="23"/>
+    </row>
+    <row r="709" spans="1:3" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A709" s="10" t="s">
+        <v>732</v>
+      </c>
+      <c r="B709" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C709" s="4"/>
+    </row>
+    <row r="710" spans="1:3" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A710" s="9" t="s">
+        <v>733</v>
+      </c>
+      <c r="B710" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C710" s="6"/>
+    </row>
+    <row r="711" spans="1:3" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A711" s="10" t="s">
+        <v>734</v>
+      </c>
+      <c r="B711" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C711" s="4"/>
+    </row>
+    <row r="712" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A712" s="9" t="s">
+        <v>735</v>
+      </c>
+      <c r="B712" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C712" s="6"/>
+    </row>
+    <row r="713" spans="1:3" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A713" s="10" t="s">
+        <v>736</v>
+      </c>
+      <c r="B713" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C713" s="4"/>
+    </row>
+    <row r="714" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A714" s="9" t="s">
+        <v>737</v>
+      </c>
+      <c r="B714" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C714" s="6"/>
+    </row>
+    <row r="715" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A715" s="19" t="s">
+        <v>738</v>
+      </c>
+      <c r="B715" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C715" s="24"/>
+    </row>
+    <row r="716" spans="1:3" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A716" s="9" t="s">
+        <v>739</v>
+      </c>
+      <c r="B716" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C716" s="6"/>
+    </row>
+    <row r="717" spans="1:3" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A717" s="10" t="s">
+        <v>740</v>
+      </c>
+      <c r="B717" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C717" s="4"/>
+    </row>
+    <row r="718" spans="1:3" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A718" s="9" t="s">
+        <v>741</v>
+      </c>
+      <c r="B718" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C718" s="6"/>
+    </row>
+    <row r="719" spans="1:3" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A719" s="10" t="s">
+        <v>742</v>
+      </c>
+      <c r="B719" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C719" s="4"/>
+    </row>
+    <row r="720" spans="1:3" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A720" s="9" t="s">
+        <v>743</v>
+      </c>
+      <c r="B720" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C720" s="6"/>
+    </row>
+    <row r="721" spans="1:3" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A721" s="10" t="s">
+        <v>744</v>
+      </c>
+      <c r="B721" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C721" s="4"/>
+    </row>
+    <row r="722" spans="1:3" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A722" s="9" t="s">
+        <v>745</v>
+      </c>
+      <c r="B722" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C722" s="6"/>
+    </row>
+    <row r="723" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A723" s="19" t="s">
+        <v>746</v>
+      </c>
+      <c r="B723" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C723" s="4"/>
+    </row>
+    <row r="724" spans="1:3" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A724" s="9" t="s">
+        <v>747</v>
+      </c>
+      <c r="B724" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C724" s="6"/>
+    </row>
+    <row r="725" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A725" s="19" t="s">
+        <v>748</v>
+      </c>
+      <c r="B725" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C725" s="24"/>
+    </row>
+    <row r="726" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A726" s="9" t="s">
+        <v>749</v>
+      </c>
+      <c r="B726" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C726" s="6"/>
+    </row>
+    <row r="727" spans="1:3" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A727" s="10" t="s">
+        <v>750</v>
+      </c>
+      <c r="B727" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C727" s="4"/>
+    </row>
+    <row r="728" spans="1:3" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A728" s="9" t="s">
+        <v>751</v>
+      </c>
+      <c r="B728" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C728" s="6"/>
+    </row>
+    <row r="729" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A729" s="10" t="s">
+        <v>752</v>
+      </c>
+      <c r="B729" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C729" s="4"/>
+    </row>
+    <row r="730" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A730" s="9" t="s">
+        <v>753</v>
+      </c>
+      <c r="B730" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C730" s="6"/>
+    </row>
+    <row r="731" spans="1:3" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A731" s="10" t="s">
+        <v>754</v>
+      </c>
+      <c r="B731" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C731" s="4"/>
+    </row>
+    <row r="732" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A732" s="9" t="s">
+        <v>755</v>
+      </c>
+      <c r="B732" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C732" s="6"/>
+    </row>
+    <row r="733" spans="1:3" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A733" s="10" t="s">
+        <v>756</v>
+      </c>
+      <c r="B733" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C733" s="4"/>
+    </row>
+    <row r="734" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A734" s="9" t="s">
+        <v>757</v>
+      </c>
+      <c r="B734" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C734" s="6"/>
+    </row>
+    <row r="735" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A735" s="10" t="s">
+        <v>758</v>
+      </c>
+      <c r="B735" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C735" s="4"/>
+    </row>
+    <row r="736" spans="1:3" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A736" s="9" t="s">
+        <v>759</v>
+      </c>
+      <c r="B736" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C736" s="6"/>
+    </row>
+    <row r="737" spans="1:3" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A737" s="10" t="s">
+        <v>760</v>
+      </c>
+      <c r="B737" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C737" s="4"/>
+    </row>
+    <row r="738" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A738" s="9" t="s">
+        <v>761</v>
+      </c>
+      <c r="B738" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C738" s="6"/>
+    </row>
+    <row r="739" spans="1:3" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A739" s="10" t="s">
+        <v>762</v>
+      </c>
+      <c r="B739" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C739" s="4"/>
+    </row>
+    <row r="740" spans="1:3" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A740" s="9" t="s">
+        <v>763</v>
+      </c>
+      <c r="B740" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C740" s="6"/>
+    </row>
+    <row r="741" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A741" s="10" t="s">
+        <v>764</v>
+      </c>
+      <c r="B741" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C741" s="4"/>
+    </row>
+    <row r="742" spans="1:3" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A742" s="9" t="s">
+        <v>765</v>
+      </c>
+      <c r="B742" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C742" s="6"/>
+    </row>
+    <row r="743" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A743" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="B743" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C743" s="4"/>
+    </row>
+    <row r="744" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A744" s="22" t="s">
+        <v>767</v>
+      </c>
+      <c r="B744" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C744" s="23"/>
+    </row>
+    <row r="745" spans="1:3" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A745" s="10" t="s">
+        <v>768</v>
+      </c>
+      <c r="B745" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C745" s="4"/>
+    </row>
+    <row r="746" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A746" s="9" t="s">
+        <v>769</v>
+      </c>
+      <c r="B746" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C746" s="6"/>
+    </row>
+    <row r="747" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A747" s="10" t="s">
+        <v>770</v>
+      </c>
+      <c r="B747" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C747" s="4"/>
+    </row>
+    <row r="748" spans="1:3" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A748" s="9" t="s">
+        <v>771</v>
+      </c>
+      <c r="B748" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C748" s="23"/>
+    </row>
+    <row r="749" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A749" s="10" t="s">
+        <v>772</v>
+      </c>
+      <c r="B749" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C749" s="4"/>
+    </row>
+    <row r="750" spans="1:3" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A750" s="9" t="s">
+        <v>773</v>
+      </c>
+      <c r="B750" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C750" s="23"/>
+    </row>
+    <row r="751" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A751" s="10" t="s">
+        <v>774</v>
+      </c>
+      <c r="B751" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C751" s="4"/>
+    </row>
+    <row r="752" spans="1:3" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A752" s="9" t="s">
+        <v>775</v>
+      </c>
+      <c r="B752" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C752" s="6"/>
+    </row>
+    <row r="753" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A753" s="10" t="s">
+        <v>776</v>
+      </c>
+      <c r="B753" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C753" s="4"/>
+    </row>
+    <row r="754" spans="1:3" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A754" s="9" t="s">
+        <v>777</v>
+      </c>
+      <c r="B754" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C754" s="6"/>
+    </row>
+    <row r="755" spans="1:3" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A755" s="10" t="s">
+        <v>778</v>
+      </c>
+      <c r="B755" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C755" s="4"/>
+    </row>
+    <row r="756" spans="1:3" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A756" s="9" t="s">
+        <v>779</v>
+      </c>
+      <c r="B756" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C756" s="6"/>
+    </row>
+    <row r="757" spans="1:3" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A757" s="10" t="s">
+        <v>780</v>
+      </c>
+      <c r="B757" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C757" s="4"/>
+    </row>
+    <row r="758" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A758" s="9" t="s">
+        <v>781</v>
+      </c>
+      <c r="B758" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C758" s="6"/>
+    </row>
+    <row r="759" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A759" s="10" t="s">
+        <v>782</v>
+      </c>
+      <c r="B759" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C759" s="4"/>
+    </row>
+    <row r="760" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A760" s="9" t="s">
+        <v>783</v>
+      </c>
+      <c r="B760" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C760" s="6"/>
+    </row>
+    <row r="761" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A761" s="10" t="s">
+        <v>784</v>
+      </c>
+      <c r="B761" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C761" s="4"/>
+    </row>
+    <row r="762" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A762" s="9" t="s">
+        <v>785</v>
+      </c>
+      <c r="B762" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C762" s="6"/>
+    </row>
+    <row r="763" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A763" s="10" t="s">
+        <v>786</v>
+      </c>
+      <c r="B763" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C763" s="4"/>
+    </row>
+    <row r="764" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A764" s="9" t="s">
+        <v>787</v>
+      </c>
+      <c r="B764" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C764" s="6"/>
+    </row>
+    <row r="765" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A765" s="10" t="s">
+        <v>788</v>
+      </c>
+      <c r="B765" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C765" s="4"/>
+    </row>
+    <row r="766" spans="1:3" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A766" s="9" t="s">
+        <v>789</v>
+      </c>
+      <c r="B766" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C766" s="6"/>
+    </row>
+    <row r="767" spans="1:3" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A767" s="10" t="s">
+        <v>790</v>
+      </c>
+      <c r="B767" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C767" s="4"/>
+    </row>
+    <row r="768" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A768" s="9" t="s">
+        <v>791</v>
+      </c>
+      <c r="B768" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C768" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>
